--- a/data_bank.xlsx
+++ b/data_bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8248DBE4-2565-497A-81A6-A836AB7823E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7422F9-51D1-4EFF-9669-A058B733361E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="112">
   <si>
     <t>Асуулт</t>
   </si>
@@ -37,9 +37,6 @@
     <t>Түвшин</t>
   </si>
   <si>
-    <t>Дараах тоонуудаас иррационал тоог сонгоно уу. 1A. $-9$ B. $5.(12)$ C. $8$ D. $\sqrt{37}$</t>
-  </si>
-  <si>
     <t>D</t>
   </si>
   <si>
@@ -49,45 +46,15 @@
     <t>Мэдлэг ойлголт</t>
   </si>
   <si>
-    <t>Рационал тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? 1, 2A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
-  </si>
-  <si>
-    <t>Бодит тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? 3, 4A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
-  </si>
-  <si>
     <t>B</t>
   </si>
   <si>
-    <t>Бүхэл тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? 2, 5A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
-  </si>
-  <si>
     <t>A</t>
   </si>
   <si>
-    <t>Натурал тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? 2, 6A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
-  </si>
-  <si>
     <t>C</t>
   </si>
   <si>
-    <t>Төгсгөлгүй, үегүй аравтын бутархайг юу гэж нэрлэдэг вэ? 4, 7A. Рационал тоо B. Иррационал тоо C. Бүхэл тоо D. Натурал тоо</t>
-  </si>
-  <si>
-    <t>$\sqrt{2}$ нь ямар төрлийн тоо вэ? 4, 8A. Натурал B. Бүхэл C. Иррационал D. Төгсгөлөг бутархай</t>
-  </si>
-  <si>
-    <t>$\pi$ тоо ямар олонлогт харьяалагдах вэ? 4, 8A. $\mathbb{N}$ B. $\mathbb{Z}$ C. $\mathbb{Q}$ D. $\mathbb{R}$ (Иррационал)</t>
-  </si>
-  <si>
-    <t>Дараах тоонуудаас бодит тоо биш тоог заана уу. 9A. $\sqrt{4}$ B. $-\sqrt{9}$ C. $\sqrt{-4}$ D. $0$</t>
-  </si>
-  <si>
-    <t>Рационал ба иррационал тоонуудын нэгдлийг юу гэх вэ? 4, 10A. Бүхэл тоо B. Бодит тоо C. Натурал тоо D. Анхны тоо</t>
-  </si>
-  <si>
-    <t>$0.625$ тоо нь ямар төрлийн тоо вэ? 9A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
-  </si>
-  <si>
     <t>$1/3$ тоог аравтын бутархайд шилжүүлбэл: 4, 8A. $0.3$ B. $0.33$ C. $0.(3)$ D. $3.0$</t>
   </si>
   <si>
@@ -356,6 +323,39 @@
   </si>
   <si>
     <t>$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга хэд вэ? 105, 106A. $5.9$ B. $6.0$ C. $5.8$ D. $5.91$</t>
+  </si>
+  <si>
+    <t>Дараах тоонуудаас иррационал тоог сонгоно уу. A. $-9$ B. $5.(12)$ C. $8$ D. $\sqrt{37}$</t>
+  </si>
+  <si>
+    <t>Рационал тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
+  </si>
+  <si>
+    <t>Бодит тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
+  </si>
+  <si>
+    <t>Бүхэл тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
+  </si>
+  <si>
+    <t>Натурал тоон олонлогийг ямар үсгээр тэмдэглэдэг вэ? A. $\mathbb{Z}$ B. $\mathbb{R}$ C. $\mathbb{N}$ D. $\mathbb{Q}$</t>
+  </si>
+  <si>
+    <t>Төгсгөлгүй, үегүй аравтын бутархайг юу гэж нэрлэдэг вэ? A. Рационал тоо B. Иррационал тоо C. Бүхэл тоо D. Натурал тоо</t>
+  </si>
+  <si>
+    <t>$\sqrt{2}$ нь ямар төрлийн тоо вэ? A. Натурал B. Бүхэл C. Иррационал D. Төгсгөлөг бутархай</t>
+  </si>
+  <si>
+    <t>$\pi$ тоо ямар олонлогт харьяалагдах вэ? A. $\mathbb{N}$ B. $\mathbb{Z}$ C. $\mathbb{Q}$ D. $\mathbb{R}$ (Иррационал)</t>
+  </si>
+  <si>
+    <t>Дараах тоонуудаас бодит тоо биш тоог заана уу. A. $\sqrt{4}$ B. $-\sqrt{9}$ C. $\sqrt{-4}$ D. $0$</t>
+  </si>
+  <si>
+    <t>Рационал ба иррационал тоонуудын нэгдлийг юу гэх вэ? A. Бүхэл тоо B. Бодит тоо C. Натурал тоо D. Анхны тоо</t>
+  </si>
+  <si>
+    <t>$0.625$ тоо нь ямар төрлийн тоо вэ? A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
   </si>
 </sst>
 </file>
@@ -401,7 +401,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -418,9 +418,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -653,7 +650,7 @@
   <cols>
     <col min="1" max="1" width="116.88671875" customWidth="1"/>
     <col min="3" max="3" width="7.21875" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" style="9" customWidth="1"/>
+    <col min="5" max="5" width="18.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
@@ -675,1412 +672,1702 @@
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C2" s="8"/>
+      <c r="C2" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D2" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>9</v>
+        <v>102</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D3" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>10</v>
+        <v>103</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="8"/>
+        <v>8</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="D4" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E4" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>12</v>
+        <v>104</v>
       </c>
       <c r="B5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="8"/>
+        <v>9</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>9</v>
+      </c>
       <c r="D5" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E5" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>14</v>
+        <v>105</v>
       </c>
       <c r="B6" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C6" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="D6" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E6" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>16</v>
+        <v>106</v>
       </c>
       <c r="B7" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="8"/>
+        <v>8</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="D7" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E7" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>17</v>
+        <v>107</v>
       </c>
       <c r="B8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C8" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="D8" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E8" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>18</v>
+        <v>108</v>
       </c>
       <c r="B9" s="7" t="s">
-        <v>6</v>
-      </c>
-      <c r="C9" s="8"/>
+        <v>5</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>5</v>
+      </c>
       <c r="D9" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E9" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>19</v>
+        <v>109</v>
       </c>
       <c r="B10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="C10" s="8"/>
+        <v>10</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>10</v>
+      </c>
       <c r="D10" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E10" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>20</v>
+        <v>110</v>
       </c>
       <c r="B11" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="C11" s="8"/>
+        <v>8</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>8</v>
+      </c>
       <c r="D11" s="6" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E11" s="6" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>21</v>
+        <v>111</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E12" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="B13" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E13" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
-        <v>23</v>
+        <v>12</v>
       </c>
       <c r="B14" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E14" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="B15" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E16" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="B17" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="3" t="s">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="B18" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E18" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
-        <v>28</v>
+        <v>17</v>
       </c>
       <c r="B19" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E19" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
-        <v>29</v>
+        <v>18</v>
       </c>
       <c r="B20" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E20" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="3" t="s">
-        <v>30</v>
+        <v>19</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="3" t="s">
-        <v>31</v>
+        <v>20</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>32</v>
+        <v>21</v>
       </c>
       <c r="B23" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E23" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="3" t="s">
-        <v>33</v>
+        <v>22</v>
       </c>
       <c r="B24" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="3" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B25" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D25" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="3" t="s">
-        <v>35</v>
+        <v>24</v>
       </c>
       <c r="B26" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D26" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E26" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="3" t="s">
-        <v>36</v>
+        <v>25</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E27" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="3" t="s">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="B28" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E28" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="3" t="s">
-        <v>38</v>
+        <v>27</v>
       </c>
       <c r="B29" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E29" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="3" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E30" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="3" t="s">
-        <v>40</v>
+        <v>29</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E31" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="3" t="s">
-        <v>41</v>
+        <v>30</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E32" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="3" t="s">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C33" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E33" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="3" t="s">
-        <v>43</v>
+        <v>32</v>
       </c>
       <c r="B34" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C34" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E34" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="3" t="s">
-        <v>44</v>
+        <v>33</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C35" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E35" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="3" t="s">
-        <v>45</v>
+        <v>34</v>
       </c>
       <c r="B36" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C36" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E36" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="3" t="s">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C37" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E37" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="3" t="s">
-        <v>47</v>
+        <v>36</v>
       </c>
       <c r="B38" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C38" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E38" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="3" t="s">
-        <v>48</v>
+        <v>37</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C39" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D39" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E39" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="3" t="s">
-        <v>49</v>
+        <v>38</v>
       </c>
       <c r="B40" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C40" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E40" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="3" t="s">
-        <v>50</v>
+        <v>39</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C41" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E41" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="3" t="s">
-        <v>51</v>
+        <v>40</v>
       </c>
       <c r="B42" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C42" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E42" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="3" t="s">
-        <v>52</v>
+        <v>41</v>
       </c>
       <c r="B43" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C43" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E43" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="3" t="s">
-        <v>53</v>
+        <v>42</v>
       </c>
       <c r="B44" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C44" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E44" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="3" t="s">
-        <v>54</v>
+        <v>43</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C45" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E45" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="3" t="s">
-        <v>55</v>
+        <v>44</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C46" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E46" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="3" t="s">
-        <v>56</v>
+        <v>45</v>
       </c>
       <c r="B47" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C47" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E47" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="3" t="s">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="B48" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C48" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E48" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="3" t="s">
-        <v>58</v>
+        <v>47</v>
       </c>
       <c r="B49" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C49" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E49" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="3" t="s">
-        <v>59</v>
+        <v>48</v>
       </c>
       <c r="B50" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C50" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E50" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="3" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="B51" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C51" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E51" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="3" t="s">
-        <v>61</v>
+        <v>50</v>
       </c>
       <c r="B52" s="4" t="s">
-        <v>6</v>
+        <v>5</v>
+      </c>
+      <c r="C52" s="4" t="s">
+        <v>5</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E52" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="3" t="s">
-        <v>62</v>
+        <v>51</v>
       </c>
       <c r="B53" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C53" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D53" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E53" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="3" t="s">
-        <v>63</v>
+        <v>52</v>
       </c>
       <c r="B54" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C54" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D54" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E54" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="3" t="s">
-        <v>64</v>
+        <v>53</v>
       </c>
       <c r="B55" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C55" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E55" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="3" t="s">
-        <v>65</v>
+        <v>54</v>
       </c>
       <c r="B56" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C56" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E56" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="3" t="s">
-        <v>66</v>
+        <v>55</v>
       </c>
       <c r="B57" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C57" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E57" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="3" t="s">
-        <v>67</v>
+        <v>56</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C58" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E58" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="3" t="s">
-        <v>68</v>
+        <v>57</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C59" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E59" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="3" t="s">
-        <v>69</v>
+        <v>58</v>
       </c>
       <c r="B60" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C60" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E60" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="3" t="s">
-        <v>70</v>
+        <v>59</v>
       </c>
       <c r="B61" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C61" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E61" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="3" t="s">
-        <v>71</v>
+        <v>60</v>
       </c>
       <c r="B62" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C62" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E62" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="3" t="s">
-        <v>72</v>
+        <v>61</v>
       </c>
       <c r="B63" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C63" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D63" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E63" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="3" t="s">
-        <v>73</v>
+        <v>62</v>
       </c>
       <c r="B64" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C64" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E64" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A65" s="3" t="s">
-        <v>74</v>
+        <v>63</v>
       </c>
       <c r="B65" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C65" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E65" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A66" s="3" t="s">
-        <v>75</v>
+        <v>64</v>
       </c>
       <c r="B66" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C66" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E66" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A67" s="3" t="s">
-        <v>76</v>
+        <v>65</v>
       </c>
       <c r="B67" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C67" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E67" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A68" s="3" t="s">
-        <v>77</v>
+        <v>66</v>
       </c>
       <c r="B68" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C68" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E68" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="69" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A69" s="3" t="s">
-        <v>78</v>
+        <v>67</v>
       </c>
       <c r="B69" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C69" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E69" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C70" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D70" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E70" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A71" s="3" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="B71" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C71" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E71" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A72" s="3" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C72" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E72" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A73" s="3" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C73" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E73" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A74" s="3" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C74" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E74" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A75" s="3" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="B75" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C75" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E75" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A76" s="3" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="B76" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C76" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E76" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A77" s="3" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="B77" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C77" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D77" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E77" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A78" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="B78" s="4" t="s">
-        <v>88</v>
+        <v>77</v>
+      </c>
+      <c r="C78" s="4" t="s">
+        <v>77</v>
       </c>
       <c r="D78" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E78" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A79" s="3" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="B79" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C79" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D79" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E79" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A80" s="3" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="B80" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C80" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D80" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E80" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="3" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="B81" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C81" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D81" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E81" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="3" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C82" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D82" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E82" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="3" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="B83" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C83" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D83" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E83" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="3" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C84" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D84" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E84" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="3" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C85" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D85" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E85" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="3" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C86" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D86" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E86" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="3" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="B87" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C87" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D87" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E87" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="3" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C88" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D88" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E88" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="3" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C89" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D89" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E89" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="B90" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C90" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D90" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E90" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="3" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C91" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D91" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E91" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="3" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C92" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D92" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E92" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="3" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="B93" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C93" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D93" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E93" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="3" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="B94" s="4" t="s">
-        <v>15</v>
+        <v>10</v>
+      </c>
+      <c r="C94" s="4" t="s">
+        <v>10</v>
       </c>
       <c r="D94" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E94" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="3" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C95" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D95" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E95" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="3" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="B96" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C96" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D96" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E96" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="3" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="B97" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C97" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D97" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E97" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="3" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C98" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D98" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E98" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="3" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="B99" s="4" t="s">
-        <v>11</v>
+        <v>8</v>
+      </c>
+      <c r="C99" s="4" t="s">
+        <v>8</v>
       </c>
       <c r="D99" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E99" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="3" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C100" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D100" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E100" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="3" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="B101" s="4" t="s">
-        <v>13</v>
+        <v>9</v>
+      </c>
+      <c r="C101" s="4" t="s">
+        <v>9</v>
       </c>
       <c r="D101" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E101" s="5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">

--- a/data_bank.xlsx
+++ b/data_bank.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DeLL\Desktop\math_project\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E7422F9-51D1-4EFF-9669-A058B733361E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6A31547C-5336-4E4A-A2F4-916CA300D2D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="505" uniqueCount="112">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="111">
   <si>
     <t>Асуулт</t>
   </si>
@@ -28,9 +28,6 @@
     <t>Хариу</t>
   </si>
   <si>
-    <t>Бодолт</t>
-  </si>
-  <si>
     <t>Нэгж</t>
   </si>
   <si>
@@ -55,276 +52,9 @@
     <t>C</t>
   </si>
   <si>
-    <t>$1/3$ тоог аравтын бутархайд шилжүүлбэл: 4, 8A. $0.3$ B. $0.33$ C. $0.(3)$ D. $3.0$</t>
-  </si>
-  <si>
-    <t>$2/9$ тоог аравтын бутархайд шилжүүлбэл: 4, 8A. $0.2$ B. $0.22$ C. $0.(2)$ D. $2.2$</t>
-  </si>
-  <si>
-    <t>$\sqrt{10}$ тоо нь иррационал тоо мөн үү? 8, 9A. Мөн B. Биш C. Натурал тоо D. Бүхэл тоо</t>
-  </si>
-  <si>
-    <t>$\mathbb{Q} \cup \mathbb{I}$ (Рационал ба Иррационал) нэгдэл нь: 4, 10A. $\mathbb{N}$ B. $\mathbb{Z}$ C. $\mathbb{R}$ D. $\emptyset$</t>
-  </si>
-  <si>
-    <t>$\sqrt{101}$ нь иррационал тоо мөн үү? 8, 9A. Мөн B. Биш C. Рационал D. Бүхэл</t>
-  </si>
-  <si>
-    <t>$1.55$ нь ямар төрлийн тоо вэ? 8A. Натурал B. Бүхэл C. Иррационал D. Рационал</t>
-  </si>
-  <si>
-    <t>$5.(12)$ нь ямар төрлийн тоо вэ? 8A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
-  </si>
-  <si>
-    <t>$\pi$ тооны ойролцоо утгыг $3.1415...$ гэж өгсөн бол тэр нь: 2, 11A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
-  </si>
-  <si>
-    <t>$22/7$ нь $\pi$ тооны ойролцоо утга бол энэ нь: 11A. Иррационал B. Рационал C. Бүхэл D. Натурал</t>
-  </si>
-  <si>
-    <t>$\sqrt{900}$ утгыг олно уу. 12, 13A. $3$ B. $30$ C. $90$ D. $300$</t>
-  </si>
-  <si>
-    <t>$\sqrt{128}$ илэрхийллийг $a\sqrt{b}$ дүрсэд бичвэл: 12, 14A. $8\sqrt{2}$ B. $2\sqrt{8}$ C. $4\sqrt{2}$ D. $64\sqrt{2}$</t>
-  </si>
-  <si>
-    <t>$-\sqrt{100}$ тооны язгуурын утгыг олоорой. 15, 16A. $10$ B. $50$ C. $-10$ D. $-50$</t>
-  </si>
-  <si>
-    <t>$(\sqrt{13})^2$ илэрхийллийн утга хэд вэ? 15, 17A. $13$ B. $-13$ C. $-169$ D. $169$</t>
-  </si>
-  <si>
-    <t>$\sqrt{6} \times \sqrt{6}$ утгыг ол. 18, 19A. $36$ B. $6$ C. $12$ D. $\sqrt{12}$</t>
-  </si>
-  <si>
-    <t>$10\sqrt{7}$ үржигдэхүүнийг язгуурын тэмдэг доор оруулбал: 20, 21A. $\sqrt{70}$ B. $\sqrt{700}$ C. $70$ D. $700$</t>
-  </si>
-  <si>
-    <t>$\sqrt{25/9}$ язгуурын утгыг олно уу. 12, 22A. $5/9$ B. $25/3$ C. $5/3$ D. $1.5$</t>
-  </si>
-  <si>
-    <t>$-\sqrt{0.16}$ утгыг олно уу. 18, 23A. $-0.16$ B. $-0.4$ C. $0.4$ D. $0.16$</t>
-  </si>
-  <si>
-    <t>$\sqrt{15^2}$ утгыг олно уу. 17, 18A. $15$ B. $225$ C. $\sqrt{15}$ D. $30$</t>
-  </si>
-  <si>
-    <t>$\sqrt{30000}$ утгыг язгуураас гаргавал: 18, 24A. $100\sqrt{3}$ B. $300$ C. $30\sqrt{10}$ D. $10\sqrt{3}$</t>
-  </si>
-  <si>
-    <t>$(\sqrt{a})^2 = a$ чанар ямар үед үнэн бэ? 12, 25A. $a &lt; 0$ B. $a \ge 0$ C. $a = 1$ D. Бүх $a$</t>
-  </si>
-  <si>
-    <t>$\sqrt{18}$ илэрхийллийг хялбарчилбал: 12, 26A. $2\sqrt{3}$ B. $3\sqrt{2}$ C. $9\sqrt{2}$ D. $2\sqrt{9}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{75}$ илэрхийллийг $a\sqrt{b}$ хэлбэрт бич. 12, 27A. $3\sqrt{5}$ B. $5\sqrt{3}$ C. $25\sqrt{3}$ D. $15\sqrt{5}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{32}$ илэрхийллийг хялбарчилбал: 12, 28A. $4\sqrt{2}$ B. $2\sqrt{4}$ C. $16\sqrt{2}$ D. $8\sqrt{4}$</t>
-  </si>
-  <si>
-    <t>$-\sqrt{0.64}$ утга хэд вэ? 3, 23A. $-0.64$ B. $-0.8$ C. $0.8$ D. $0.64$</t>
-  </si>
-  <si>
-    <t>$\sqrt{242}$ илэрхийллийг хялбарчил. 12, 29A. $11\sqrt{2}$ B. $2\sqrt{11}$ C. $121\sqrt{2}$ D. $22\sqrt{2}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{98}$ илэрхийллийг хялбарчил. 12, 16A. $7\sqrt{2}$ B. $2\sqrt{7}$ C. $49\sqrt{2}$ D. $14\sqrt{2}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{180}$ илэрхийллийг хялбарчил. 18, 30A. $6\sqrt{5}$ B. $5\sqrt{6}$ C. $36\sqrt{5}$ D. $10\sqrt{18}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{54}$ илэрхийллийг хялбарчил. 18, 31A. $3\sqrt{6}$ B. $6\sqrt{3}$ C. $9\sqrt{6}$ D. $2\sqrt{27}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{64/49}$ утгыг ол. 12, 32A. $8/49$ B. $64/7$ C. $8/7$ D. $1.1$</t>
-  </si>
-  <si>
-    <t>$\sqrt{36/169}$ утгыг ол. 33, 34A. $6/13$ B. $36/13$ C. $6/169$ D. $0.5$</t>
-  </si>
-  <si>
-    <t>$\sqrt{81/4}$ утгыг ол. 33, 35A. $9/4$ B. $81/2$ C. $9/2$ D. $4.5$</t>
-  </si>
-  <si>
-    <t>$0.6\sqrt{6}$ тоог язгуурын тэмдэг доор оруул. 36, 37A. $\sqrt{3.6}$ B. $\sqrt{2.16}$ C. $\sqrt{0.36}$ D. $\sqrt{36}$</t>
-  </si>
-  <si>
-    <t>$8\sqrt{5}$ тоог язгуурын тэмдэг доор оруул. 38, 39A. $\sqrt{40}$ B. $\sqrt{320}$ C. $\sqrt{160}$ D. $\sqrt{85}$</t>
-  </si>
-  <si>
-    <t>$\sqrt{144} - \sqrt{100}$ утга хэд вэ? 12, 40A. $44$ B. $12$ C. $10$ D. $2$</t>
-  </si>
-  <si>
-    <t>$\sqrt{6} + \sqrt{3}$ ерөнхий үржигдэхүүн хаалтнаас гарга. 15, 41A. $3(\sqrt{2}+1)$ B. $\sqrt{3}(\sqrt{2}+1)$ C. $\sqrt{2}(\sqrt{3}+1)$ D. $3(2+1)$</t>
-  </si>
-  <si>
-    <t>$\sqrt{15} - \sqrt{10}$ ерөнхий үржигдэхүүн хаалтнаас гарга. 38, 42A. $5(\sqrt{3}-\sqrt{2})$ B. $\sqrt{5}(3-2)$ C. $\sqrt{5}(\sqrt{3}-\sqrt{2})$ D. $3(\sqrt{5}-\sqrt{2})$</t>
-  </si>
-  <si>
-    <t>$\sqrt{21} + \sqrt{14}$ ерөнхий үржигдэхүүн хаалтнаас гарга. 36A. $7(\sqrt{3}+\sqrt{2})$ B. $\sqrt{7}(\sqrt{3}+\sqrt{2})$ C. $\sqrt{3}(7+2)$ D. $\sqrt{14}(\sqrt{1.5}+1)$</t>
-  </si>
-  <si>
-    <t>$\sqrt{3} \times \sqrt{3}$ утга хэд вэ? 12, 43A. $9$ B. $3$ C. $\sqrt{9}$ D. $1$</t>
-  </si>
-  <si>
-    <t>$(\sqrt{16})^2$ утга хэд вэ? 18, 44A. $4$ B. $16$ C. $256$ D. $\sqrt{16}$</t>
-  </si>
-  <si>
-    <t>$120,000$ тоог стандарт дүрсэд бичсэн хэлбэрийг ол. 45, 46A. $12 \times 10^4$ B. $1.2 \times 10^4$ C. $12 \times 10^5$ D. $1.2 \times 10^5$</t>
-  </si>
-  <si>
-    <t>$0.00000234$ тоог стандарт дүрсэд бич. 47, 48A. $2.34 \times 10^{-6}$ B. $2.34 \times 10^6$ C. $2.34 \times 10^{-8}$ D. $2.34 \times 10^8$</t>
-  </si>
-  <si>
-    <t>$5.83 \times 10^9$ тоог дэлгэрэнгүй хэлбэрт бич. 45, 49A. $5,830,000,000$ B. $583,000,000$ C. $5,830,000$ D. $5.83$</t>
-  </si>
-  <si>
-    <t>$9.0 \times 10^{-4}$ аравтын бутархай хэлбэрт бич. 45, 50A. $9000$ B. $0.00009$ C. $0.0009$ D. $0.009$</t>
-  </si>
-  <si>
-    <t>$520,000,000$ тоог стандарт дүрсэд бич. 51, 52A. $5.2 \times 10^7$ B. $5.2 \times 10^8$ C. $52 \times 10^7$ D. $0.52 \times 10^9$</t>
-  </si>
-  <si>
-    <t>$1.08 \times 10^6$ тоог дэлгэрэнгүй хэлбэрт бич. 51, 53A. $1,080,000$ B. $108,000$ C. $10,800,000$ D. $1.08$</t>
-  </si>
-  <si>
-    <t>$7,100,000$ тоог стандарт дүрсэд бич. 54, 55A. $7.1 \times 10^6$ B. $7.1 \times 10^5$ C. $71 \times 10^5$ D. $71 \times 10^6$</t>
-  </si>
-  <si>
-    <t>$9.2 \times 10^{11}$ тоог дэлгэрэнгүй хэлбэрт бич. 54, 56A. $920,000,000,000$ B. $9,200,000,000$ C. $92,000,000,000$ D. $9.2$</t>
-  </si>
-  <si>
-    <t>$2.1 \times 10^{-5}$ аравтын бутархай хэлбэрт бич. 57, 58A. $0.00021$ B. $0.000021$ C. $0.0000021$ D. $0.0021$</t>
-  </si>
-  <si>
-    <t>$7^{14} \times 7^{-12}$ илэрхийллийн утгыг олоорой. 15, 59A. $7^{26}$ B. $7^{-26}$ C. $7^2$ D. $49$</t>
-  </si>
-  <si>
-    <t>$100 \div 10^{-3}$ утгыг ол. 38, 60A. $1000$ B. $10^5$ C. $1$ D. $3$</t>
-  </si>
-  <si>
-    <t>$9^{-8} \div 9^{-9}$ утга хэд вэ? 36, 61A. $9$ B. $0$ C. $1$ D. $9^{-17}$</t>
-  </si>
-  <si>
-    <t>$0.000064$ тоог стандарт дүрсэд бич. 62, 63A. $6.4 \times 10^{-5}$ B. $64 \times 10^{-6}$ C. $0.64 \times 10^4$ D. $6.4 \times 10^5$</t>
-  </si>
-  <si>
-    <t>$5.03 \times 10^{-7}$ аравтын бутархайгаар бич. 64, 65A. $0.000000503$ B. $0.00000503$ C. $0.0000000503$ D. $503,000$</t>
-  </si>
-  <si>
-    <t>$10^{-4}$ утга хэд вэ? 66, 67A. $0.001$ B. $0.0001$ C. $10000$ D. $0.00001$</t>
-  </si>
-  <si>
-    <t>$2.1 \times 10^8$ утга хэд вэ? 66, 68A. $210,000,000$ B. $21,000,000$ C. $2,100,000,000$ D. $0.000000021$</t>
-  </si>
-  <si>
-    <t>$7.196 \times 10^5$ утга хэд вэ? 66, 69A. $719,600$ B. $7,196,000$ C. $71,960$ D. $719.6$</t>
-  </si>
-  <si>
-    <t>$4.5 \times 10^{-4}$ утга хэд вэ? 66, 70A. $0.00045$ B. $0.0045$ C. $0.000045$ D. $45,000$</t>
-  </si>
-  <si>
-    <t>$275.02 \times 10^{-3}$ утга хэд вэ? 66, 71A. $0.27502$ B. $2.7502$ C. $0.027502$ D. $275,020$</t>
-  </si>
-  <si>
-    <t>$0.000000000076$ стандарт дүрсэд бич. 72, 73A. $7.6 \times 10^{-11}$ B. $7.6 \times 10^{-10}$ C. $0.76 \times 10^{-11}$ D. $76 \times 10^{-12}$</t>
-  </si>
-  <si>
-    <t>$1.2 \times 10^5$ дэлгэрэнгүй бичвэл: 46, 66A. $12,000$ B. $120,000$ C. $1,200,000$ D. $120$</t>
-  </si>
-  <si>
-    <t>$10^0$ утга хэд вэ? 66A. $0$ B. $1$ C. $10$ D. Тодорхойгүй</t>
-  </si>
-  <si>
-    <t>$10^{-k}$ илэрхийллийг яаж бичиж болох вэ? 74, 75A. $-10^k$ B. $1/10^k$ C. $k/10$ D. $10/k$</t>
-  </si>
-  <si>
-    <t>$3.7 \times 10^5$ утга хэд вэ? 76, 77A. $37,000$ B. $370,000$ C. $3,700,000$ D. $3,700$</t>
-  </si>
-  <si>
-    <t>$8.5 \times 10^3$ утга хэд вэ? 76, 78A. $850$ B. $8,500$ C. $85,000$ D. $8.5$</t>
-  </si>
-  <si>
-    <t>$325.78$ тоог гурван тэмдэгтээр тоймло. 45, 79A. $326.0$ B. $330.0$ C. $325.8$ D. $325.7$</t>
-  </si>
-  <si>
-    <t>$90$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. 1, 80A. $9.5$ B. $9$ C. $9.4$ D. $9.48$</t>
-  </si>
-  <si>
     <t xml:space="preserve">A </t>
   </si>
   <si>
-    <t>$\sqrt{42}$ ямар хоёр бүхэл тооны хооронд орших вэ? 1, 81A. $7$ ба $8$ B. $6$ ба $7$ C. $41$ ба $43$ D. $5$ ба $6$</t>
-  </si>
-  <si>
-    <t>$57.2468$ тоог гурван тэмдэгтээр тоймло. 51, 82A. $57.24$ B. $57.2$ C. $56.2$ D. $57.3$</t>
-  </si>
-  <si>
-    <t>$4.3465$ тоог гурван тэмдэгтээр тоймло. 57, 83A. $4.30$ B. $4.34$ C. $4.35$ D. $4.40$</t>
-  </si>
-  <si>
-    <t>$29.119$ тоог $0.1$ нарийвчлалтай тоймло. 84, 85A. $29.1$ B. $29.2$ C. $29.12$ D. $29$</t>
-  </si>
-  <si>
-    <t>$6.4567$ тоог $0.001$ нарийвчлалтай тоймло. 84, 86A. $6.456$ B. $6.457$ C. $6.46$ D. $6.5$</t>
-  </si>
-  <si>
-    <t>$0.06754$ тоог хоёр тэмдэгтээр тоймло. 87, 88A. $0.06$ B. $0.068$ C. $0.07$ D. $0.067$</t>
-  </si>
-  <si>
-    <t>$\sqrt{11}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. 6, 89A. $3.3$ B. $3$ C. $4$ D. $3.32$</t>
-  </si>
-  <si>
-    <t>$\sqrt{27}$ ямар хоёр бүхэл тооны хооронд орших вэ? 3, 90A. $5$ ба $6$ B. $6$ ба $7$ C. $27$ ба $28$ D. $4$ ба $5$</t>
-  </si>
-  <si>
-    <t>$\sqrt{15}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. 3, 91A. $4$ B. $3.9$ C. $3$ D. $3.8$</t>
-  </si>
-  <si>
-    <t>$\sqrt{50}$ ямар хоёр бүхэл тооны хооронд орших вэ? 81, 92A. $50$ ба $51$ B. $6$ ба $7$ C. $7$ ба $8$ D. $5$ ба $6$</t>
-  </si>
-  <si>
-    <t>$148$ тоог аравтаар тоймло. 87, 93A. $140$ B. $150$ C. $100$ D. $200$</t>
-  </si>
-  <si>
-    <t>$3215$ тоог зуутаар тоймло. 87, 94A. $3200$ B. $3220$ C. $3300$ D. $3000$</t>
-  </si>
-  <si>
-    <t>$5679$ тоог мянгатаар тоймло. 87, 95A. $5000$ B. $5700$ C. $6000$ D. $5600$</t>
-  </si>
-  <si>
-    <t>$0.00048837$ тоог 1 тэмдэгтээр тоймло. 96, 97A. $0.1$ B. $0$ C. $0.0005$ D. $0.0004$</t>
-  </si>
-  <si>
-    <t>$\sqrt{80}$ ямар хоёр бүхэл тооны хооронд орших вэ? 5, 98A. $80$ ба $81$ B. $8$ ба $9$ C. $7$ ба $8$ D. $9$ ба $10$</t>
-  </si>
-  <si>
-    <t>$\sqrt{40}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. 5, 99A. $20$ B. $6.32$ C. $6.3$ D. $6.4$</t>
-  </si>
-  <si>
-    <t>$0.06754$ тоог нэг тэмдэгтээр тоймло. 87, 97A. $0.06$ B. $0.07$ C. $0.1$ D. $0$</t>
-  </si>
-  <si>
-    <t>$213.67$ тоог $0.1$ нарийвчлалтай тоймло. 87A. $213.6$ B. $213.7$ C. $214$ D. $213.67$</t>
-  </si>
-  <si>
-    <t>$65.1359$ тоог $0.01$ нарийвчлалтай тоймло. 87A. $65.13$ B. $65.14$ C. $65.1$ D. $65.136$</t>
-  </si>
-  <si>
-    <t>$0.00025648$ тоог гурван тэмдэгтээр тоймло. 87, 100A. $0.000256$ B. $0.000257$ C. $0.0003$ D. $0.0002565$</t>
-  </si>
-  <si>
-    <t>$\sqrt{133}$ ямар хоёр бүхэл тооны хооронд орших вэ? 101, 102A. $10$ ба $11$ B. $11$ ба $12$ C. $12$ ба $13$ D. $13$ ба $14$</t>
-  </si>
-  <si>
-    <t>$2\sqrt{17}$ ямар хоёр бүхэл тооны хооронд орших вэ? 103, 104A. $8$ ба $9$ B. $7$ ба $8$ C. $9$ ба $10$ D. $2$ ба $3$</t>
-  </si>
-  <si>
-    <t>$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга хэд вэ? 105, 106A. $5.9$ B. $6.0$ C. $5.8$ D. $5.91$</t>
-  </si>
-  <si>
     <t>Дараах тоонуудаас иррационал тоог сонгоно уу. A. $-9$ B. $5.(12)$ C. $8$ D. $\sqrt{37}$</t>
   </si>
   <si>
@@ -356,6 +86,273 @@
   </si>
   <si>
     <t>$0.625$ тоо нь ямар төрлийн тоо вэ? A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
+  </si>
+  <si>
+    <t>$1/3$ тоог аравтын бутархайд шилжүүлбэл: A. $0.3$ B. $0.33$ C. $0.(3)$ D. $3.0$</t>
+  </si>
+  <si>
+    <t>$2/9$ тоог аравтын бутархайд шилжүүлбэл: A. $0.2$ B. $0.22$ C. $0.(2)$ D. $2.2$</t>
+  </si>
+  <si>
+    <t>$\sqrt{10}$ тоо нь иррационал тоо мөн үү? A. Мөн B. Биш C. Натурал тоо D. Бүхэл тоо</t>
+  </si>
+  <si>
+    <t>$\mathbb{Q} \cup \mathbb{I}$ (Рационал ба Иррационал) нэгдэл нь: A. $\mathbb{N}$ B. $\mathbb{Z}$ C. $\mathbb{R}$ D. $\emptyset$</t>
+  </si>
+  <si>
+    <t>$\sqrt{101}$ нь иррационал тоо мөн үү? A. Мөн B. Биш C. Рационал D. Бүхэл</t>
+  </si>
+  <si>
+    <t>$1.55$ нь ямар төрлийн тоо вэ? A. Натурал B. Бүхэл C. Иррационал D. Рационал</t>
+  </si>
+  <si>
+    <t>$5.(12)$ нь ямар төрлийн тоо вэ? A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
+  </si>
+  <si>
+    <t>$\pi$ тооны ойролцоо утгыг $3.1415...$ гэж өгсөн бол тэр нь: A. Рационал B. Иррационал C. Бүхэл D. Натурал</t>
+  </si>
+  <si>
+    <t>$22/7$ нь $\pi$ тооны ойролцоо утга бол энэ нь: A. Иррационал B. Рационал C. Бүхэл D. Натурал</t>
+  </si>
+  <si>
+    <t>$\sqrt{900}$ утгыг олно уу. A. $3$ B. $30$ C. $90$ D. $300$</t>
+  </si>
+  <si>
+    <t>$\sqrt{128}$ илэрхийллийг $a\sqrt{b}$ дүрсэд бичвэл: A. $8\sqrt{2}$ B. $2\sqrt{8}$ C. $4\sqrt{2}$ D. $64\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$-\sqrt{100}$ тооны язгуурын утгыг олоорой. A. $10$ B. $50$ C. $-10$ D. $-50$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{13})^2$ илэрхийллийн утга хэд вэ? A. $13$ B. $-13$ C. $-169$ D. $169$</t>
+  </si>
+  <si>
+    <t>$\sqrt{6} \times \sqrt{6}$ утгыг ол. A. $36$ B. $6$ C. $12$ D. $\sqrt{12}$</t>
+  </si>
+  <si>
+    <t>$10\sqrt{7}$ үржигдэхүүнийг язгуурын тэмдэг доор оруулбал: A. $\sqrt{70}$ B. $\sqrt{700}$ C. $70$ D. $700$</t>
+  </si>
+  <si>
+    <t>$\sqrt{35}$ тооны $0.1$ нарийвчлалтай дутагдалтай ойролцоо утга хэд вэ? A. $5.9$ B. $6.0$ C. $5.8$ D. $5.91$</t>
+  </si>
+  <si>
+    <t>$2\sqrt{17}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $8$ ба $9$ B. $7$ ба $8$ C. $9$ ба $10$ D. $2$ ба $3$</t>
+  </si>
+  <si>
+    <t>$\sqrt{133}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $10$ ба $11$ B. $11$ ба $12$ C. $12$ ба $13$ D. $13$ ба $14$</t>
+  </si>
+  <si>
+    <t>$0.00025648$ тоог гурван тэмдэгтээр тоймло. A. $0.000256$ B. $0.000257$ C. $0.0003$ D. $0.0002565$</t>
+  </si>
+  <si>
+    <t>$65.1359$ тоог $0.01$ нарийвчлалтай тоймло. A. $65.13$ B. $65.14$ C. $65.1$ D. $65.136$</t>
+  </si>
+  <si>
+    <t>$213.67$ тоог $0.1$ нарийвчлалтай тоймло. A. $213.6$ B. $213.7$ C. $214$ D. $213.67$</t>
+  </si>
+  <si>
+    <t>$0.06754$ тоог нэг тэмдэгтээр тоймло. A. $0.06$ B. $0.07$ C. $0.1$ D. $0$</t>
+  </si>
+  <si>
+    <t>$\sqrt{40}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. A. $20$ B. $6.32$ C. $6.3$ D. $6.4$</t>
+  </si>
+  <si>
+    <t>$\sqrt{80}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $80$ ба $81$ B. $8$ ба $9$ C. $7$ ба $8$ D. $9$ ба $10$</t>
+  </si>
+  <si>
+    <t>$0.00048837$ тоог 1 тэмдэгтээр тоймло. A. $0.1$ B. $0$ C. $0.0005$ D. $0.0004$</t>
+  </si>
+  <si>
+    <t>$5679$ тоог мянгатаар тоймло. A. $5000$ B. $5700$ C. $6000$ D. $5600$</t>
+  </si>
+  <si>
+    <t>$3215$ тоог зуутаар тоймло. A. $3200$ B. $3220$ C. $3300$ D. $3000$</t>
+  </si>
+  <si>
+    <t>$148$ тоог аравтаар тоймло. A. $140$ B. $150$ C. $100$ D. $200$</t>
+  </si>
+  <si>
+    <t>$\sqrt{50}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $50$ ба $51$ B. $6$ ба $7$ C. $7$ ба $8$ D. $5$ ба $6$</t>
+  </si>
+  <si>
+    <t>$\sqrt{15}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. A. $4$ B. $3.9$ C. $3$ D. $3.8$</t>
+  </si>
+  <si>
+    <t>$\sqrt{27}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $5$ ба $6$ B. $6$ ба $7$ C. $27$ ба $28$ D. $4$ ба $5$</t>
+  </si>
+  <si>
+    <t>$\sqrt{11}$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. A. $3.3$ B. $3$ C. $4$ D. $3.32$</t>
+  </si>
+  <si>
+    <t>$0.06754$ тоог хоёр тэмдэгтээр тоймло. A. $0.06$ B. $0.068$ C. $0.07$ D. $0.067$</t>
+  </si>
+  <si>
+    <t>$6.4567$ тоог $0.001$ нарийвчлалтай тоймло. A. $6.456$ B. $6.457$ C. $6.46$ D. $6.5$</t>
+  </si>
+  <si>
+    <t>$29.119$ тоог $0.1$ нарийвчлалтай тоймло. A. $29.1$ B. $29.2$ C. $29.12$ D. $29$</t>
+  </si>
+  <si>
+    <t>$4.3465$ тоог гурван тэмдэгтээр тоймло. A. $4.30$ B. $4.34$ C. $4.35$ D. $4.40$</t>
+  </si>
+  <si>
+    <t>$57.2468$ тоог гурван тэмдэгтээр тоймло. A. $57.24$ B. $57.2$ C. $56.2$ D. $57.3$</t>
+  </si>
+  <si>
+    <t>$\sqrt{42}$ ямар хоёр бүхэл тооны хооронд орших вэ? A. $7$ ба $8$ B. $6$ ба $7$ C. $41$ ба $43$ D. $5$ ба $6$</t>
+  </si>
+  <si>
+    <t>$90$ тооны ойролцоо утгыг $0.1$ нарийвчлалтай ол. A. $9.5$ B. $9$ C. $9.4$ D. $9.48$</t>
+  </si>
+  <si>
+    <t>$325.78$ тоог гурван тэмдэгтээр тоймло. A. $326.0$ B. $330.0$ C. $325.8$ D. $325.7$</t>
+  </si>
+  <si>
+    <t>$8.5 \times 10^3$ утга хэд вэ? A. $850$ B. $8,500$ C. $85,000$ D. $8.5$</t>
+  </si>
+  <si>
+    <t>$3.7 \times 10^5$ утга хэд вэ? A. $37,000$ B. $370,000$ C. $3,700,000$ D. $3,700$</t>
+  </si>
+  <si>
+    <t>$10^{-k}$ илэрхийллийг яаж бичиж болох вэ? A. $-10^k$ B. $1/10^k$ C. $k/10$ D. $10/k$</t>
+  </si>
+  <si>
+    <t>$10^0$ утга хэд вэ? A. $0$ B. $1$ C. $10$ D. Тодорхойгүй</t>
+  </si>
+  <si>
+    <t>$1.2 \times 10^5$ дэлгэрэнгүй бичвэл: A. $12,000$ B. $120,000$ C. $1,200,000$ D. $120$</t>
+  </si>
+  <si>
+    <t>$0.000000000076$ стандарт дүрсэд бич. A. $7.6 \times 10^{-11}$ B. $7.6 \times 10^{-10}$ C. $0.76 \times 10^{-11}$ D. $76 \times 10^{-12}$</t>
+  </si>
+  <si>
+    <t>$275.02 \times 10^{-3}$ утга хэд вэ? A. $0.27502$ B. $2.7502$ C. $0.027502$ D. $275,020$</t>
+  </si>
+  <si>
+    <t>$4.5 \times 10^{-4}$ утга хэд вэ? A. $0.00045$ B. $0.0045$ C. $0.000045$ D. $45,000$</t>
+  </si>
+  <si>
+    <t>$7.196 \times 10^5$ утга хэд вэ? A. $719,600$ B. $7,196,000$ C. $71,960$ D. $719.6$</t>
+  </si>
+  <si>
+    <t>$2.1 \times 10^8$ утга хэд вэ? A. $210,000,000$ B. $21,000,000$ C. $2,100,000,000$ D. $0.000000021$</t>
+  </si>
+  <si>
+    <t>$10^{-4}$ утга хэд вэ? A. $0.001$ B. $0.0001$ C. $10000$ D. $0.00001$</t>
+  </si>
+  <si>
+    <t>$5.03 \times 10^{-7}$ аравтын бутархайгаар бич. A. $0.000000503$ B. $0.00000503$ C. $0.0000000503$ D. $503,000$</t>
+  </si>
+  <si>
+    <t>$0.000064$ тоог стандарт дүрсэд бич. A. $6.4 \times 10^{-5}$ B. $64 \times 10^{-6}$ C. $0.64 \times 10^4$ D. $6.4 \times 10^5$</t>
+  </si>
+  <si>
+    <t>$9^{-8} \div 9^{-9}$ утга хэд вэ? A. $9$ B. $0$ C. $1$ D. $9^{-17}$</t>
+  </si>
+  <si>
+    <t>$100 \div 10^{-3}$ утгыг ол. A. $1000$ B. $10^5$ C. $1$ D. $3$</t>
+  </si>
+  <si>
+    <t>$7^{14} \times 7^{-12}$ илэрхийллийн утгыг олоорой. A. $7^{26}$ B. $7^{-26}$ C. $7^2$ D. $49$</t>
+  </si>
+  <si>
+    <t>$2.1 \times 10^{-5}$ аравтын бутархай хэлбэрт бич. A. $0.00021$ B. $0.000021$ C. $0.0000021$ D. $0.0021$</t>
+  </si>
+  <si>
+    <t>$9.2 \times 10^{11}$ тоог дэлгэрэнгүй хэлбэрт бич. A. $920,000,000,000$ B. $9,200,000,000$ C. $92,000,000,000$ D. $9.2$</t>
+  </si>
+  <si>
+    <t>$7,100,000$ тоог стандарт дүрсэд бич. A. $7.1 \times 10^6$ B. $7.1 \times 10^5$ C. $71 \times 10^5$ D. $71 \times 10^6$</t>
+  </si>
+  <si>
+    <t>$1.08 \times 10^6$ тоог дэлгэрэнгүй хэлбэрт бич. A. $1,080,000$ B. $108,000$ C. $10,800,000$ D. $1.08$</t>
+  </si>
+  <si>
+    <t>$520,000,000$ тоог стандарт дүрсэд бич. A. $5.2 \times 10^7$ B. $5.2 \times 10^8$ C. $52 \times 10^7$ D. $0.52 \times 10^9$</t>
+  </si>
+  <si>
+    <t>$9.0 \times 10^{-4}$ аравтын бутархай хэлбэрт бич. A. $9000$ B. $0.00009$ C. $0.0009$ D. $0.009$</t>
+  </si>
+  <si>
+    <t>$5.83 \times 10^9$ тоог дэлгэрэнгүй хэлбэрт бич. A. $5,830,000,000$ B. $583,000,000$ C. $5,830,000$ D. $5.83$</t>
+  </si>
+  <si>
+    <t>$0.00000234$ тоог стандарт дүрсэд бич. A. $2.34 \times 10^{-6}$ B. $2.34 \times 10^6$ C. $2.34 \times 10^{-8}$ D. $2.34 \times 10^8$</t>
+  </si>
+  <si>
+    <t>$120,000$ тоог стандарт дүрсэд бичсэн хэлбэрийг ол. A. $12 \times 10^4$ B. $1.2 \times 10^4$ C. $12 \times 10^5$ D. $1.2 \times 10^5$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{16})^2$ утга хэд вэ? A. $4$ B. $16$ C. $256$ D. $\sqrt{16}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{3} \times \sqrt{3}$ утга хэд вэ? A. $9$ B. $3$ C. $\sqrt{9}$ D. $1$</t>
+  </si>
+  <si>
+    <t>$\sqrt{21} + \sqrt{14}$ ерөнхий үржигдэхүүн хаалтнаас гарга. A. $7(\sqrt{3}+\sqrt{2})$ B. $\sqrt{7}(\sqrt{3}+\sqrt{2})$ C. $\sqrt{3}(7+2)$ D. $\sqrt{14}(\sqrt{1.5}+1)$</t>
+  </si>
+  <si>
+    <t>$\sqrt{15} - \sqrt{10}$ ерөнхий үржигдэхүүн хаалтнаас гарга. A. $5(\sqrt{3}-\sqrt{2})$ B. $\sqrt{5}(3-2)$ C. $\sqrt{5}(\sqrt{3}-\sqrt{2})$ D. $3(\sqrt{5}-\sqrt{2})$</t>
+  </si>
+  <si>
+    <t>$\sqrt{6} + \sqrt{3}$ ерөнхий үржигдэхүүн хаалтнаас гарга. A. $3(\sqrt{2}+1)$ B. $\sqrt{3}(\sqrt{2}+1)$ C. $\sqrt{2}(\sqrt{3}+1)$ D. $3(2+1)$</t>
+  </si>
+  <si>
+    <t>$\sqrt{144} - \sqrt{100}$ утга хэд вэ? A. $44$ B. $12$ C. $10$ D. $2$</t>
+  </si>
+  <si>
+    <t>$8\sqrt{5}$ тоог язгуурын тэмдэг доор оруул. A. $\sqrt{40}$ B. $\sqrt{320}$ C. $\sqrt{160}$ D. $\sqrt{85}$</t>
+  </si>
+  <si>
+    <t>$0.6\sqrt{6}$ тоог язгуурын тэмдэг доор оруул. A. $\sqrt{3.6}$ B. $\sqrt{2.16}$ C. $\sqrt{0.36}$ D. $\sqrt{36}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{81/4}$ утгыг ол. A. $9/4$ B. $81/2$ C. $9/2$ D. $4.5$</t>
+  </si>
+  <si>
+    <t>$\sqrt{25/9}$ язгуурын утгыг олно уу. A. $5/9$ B. $25/3$ C. $5/3$ D. $1.5$</t>
+  </si>
+  <si>
+    <t>$-\sqrt{0.16}$ утгыг олно уу. A. $-0.16$ B. $-0.4$ C. $0.4$ D. $0.16$</t>
+  </si>
+  <si>
+    <t>$\sqrt{15^2}$ утгыг олно уу. A. $15$ B. $225$ C. $\sqrt{15}$ D. $30$</t>
+  </si>
+  <si>
+    <t>$\sqrt{30000}$ утгыг язгуураас гаргавал: A. $100\sqrt{3}$ B. $300$ C. $30\sqrt{10}$ D. $10\sqrt{3}$</t>
+  </si>
+  <si>
+    <t>$(\sqrt{a})^2 = a$ чанар ямар үед үнэн бэ? A. $a &lt; 0$ B. $a \ge 0$ C. $a = 1$ D. Бүх $a$</t>
+  </si>
+  <si>
+    <t>$\sqrt{18}$ илэрхийллийг хялбарчилбал: A. $2\sqrt{3}$ B. $3\sqrt{2}$ C. $9\sqrt{2}$ D. $2\sqrt{9}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{75}$ илэрхийллийг $a\sqrt{b}$ хэлбэрт бич. A. $3\sqrt{5}$ B. $5\sqrt{3}$ C. $25\sqrt{3}$ D. $15\sqrt{5}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{32}$ илэрхийллийг хялбарчилбал: A. $4\sqrt{2}$ B. $2\sqrt{4}$ C. $16\sqrt{2}$ D. $8\sqrt{4}$</t>
+  </si>
+  <si>
+    <t>$-\sqrt{0.64}$ утга хэд вэ? A. $-0.64$ B. $-0.8$ C. $0.8$ D. $0.64$</t>
+  </si>
+  <si>
+    <t>$\sqrt{242}$ илэрхийллийг хялбарчил. A. $11\sqrt{2}$ B. $2\sqrt{11}$ C. $121\sqrt{2}$ D. $22\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{98}$ илэрхийллийг хялбарчил. 6A. $7\sqrt{2}$ B. $2\sqrt{7}$ C. $49\sqrt{2}$ D. $14\sqrt{2}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{180}$ илэрхийллийг хялбарчил. A. $6\sqrt{5}$ B. $5\sqrt{6}$ C. $36\sqrt{5}$ D. $10\sqrt{18}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{54}$ илэрхийллийг хялбарчил. A. $3\sqrt{6}$ B. $6\sqrt{3}$ C. $9\sqrt{6}$ D. $2\sqrt{27}$</t>
+  </si>
+  <si>
+    <t>$\sqrt{64/49}$ утгыг ол. A. $8/49$ B. $64/7$ C. $8/7$ D. $1.1$</t>
+  </si>
+  <si>
+    <t>$\sqrt{36/169}$ утгыг ол. A. $6/13$ B. $36/13$ C. $6/169$ D. $0.5$</t>
   </si>
 </sst>
 </file>
@@ -645,15 +642,14 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:E999"/>
+  <dimension ref="A1:D999"/>
   <sheetFormatPr defaultColWidth="12.6640625" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="116.88671875" customWidth="1"/>
-    <col min="3" max="3" width="7.21875" customWidth="1"/>
-    <col min="5" max="5" width="18.5546875" style="8" customWidth="1"/>
+    <col min="4" max="4" width="18.5546875" style="8" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -666,1741 +662,1438 @@
       <c r="D1" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="6" t="s">
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="3" t="s">
+      <c r="C2" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C4" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="C5" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C7" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>4</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="C11" s="6" t="s">
+        <v>5</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A14" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A15" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A16" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A17" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C18" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C19" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A23" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="B24" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D24" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="25" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A25" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="B25" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D25" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="26" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A26" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B26" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="27" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A27" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="B27" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="28" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A28" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="B28" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="29" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A29" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="B29" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C29" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A30" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="B30" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C30" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A31" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="B31" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A32" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="B32" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D32" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="33" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A33" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="B2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E2" s="6" t="s">
+      <c r="B33" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+      <c r="C33" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A34" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="B3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E3" s="6" t="s">
+      <c r="B34" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+      <c r="C34" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D34" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A35" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B35" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C35" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D35" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="36" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A36" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B36" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D36" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A37" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="B37" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E4" s="6" t="s">
+      <c r="C37" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D37" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A38" s="3" t="s">
+        <v>106</v>
+      </c>
+      <c r="B38" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D38" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="39" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A39" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B39" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D39" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="40" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A40" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="B40" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D40" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="41" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A41" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="B41" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D41" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="42" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A42" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B42" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D42" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="43" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A43" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="B43" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C43" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D43" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="44" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A44" s="3" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
-        <v>104</v>
-      </c>
-      <c r="B5" s="7" t="s">
+      <c r="C44" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D44" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A45" s="3" t="s">
+        <v>93</v>
+      </c>
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C45" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D45" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="46" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A46" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="B46" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D46" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="47" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A47" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="B47" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D47" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A48" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="B48" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C5" s="7" t="s">
+      <c r="C48" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D48" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="49" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A49" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="B49" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C49" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D49" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="50" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A50" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="B50" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C50" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D50" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="51" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A51" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="B51" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D51" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="52" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A52" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="B52" s="4" t="s">
+        <v>4</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D52" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="53" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A53" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B53" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C53" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D53" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="54" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A54" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="B54" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D54" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="55" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A55" s="3" t="s">
+        <v>83</v>
+      </c>
+      <c r="B55" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E5" s="6" t="s">
+      <c r="C55" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D55" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="56" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A56" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="B56" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
-        <v>105</v>
-      </c>
-      <c r="B6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E6" s="6" t="s">
+      <c r="C56" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D56" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="57" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A57" s="3" t="s">
+        <v>81</v>
+      </c>
+      <c r="B57" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D57" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="58" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A58" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="B58" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D58" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="59" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A59" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="B59" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C59" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="60" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A60" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="B60" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="B7" s="7" t="s">
+      <c r="C60" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D60" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="61" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A61" s="3" t="s">
+        <v>77</v>
+      </c>
+      <c r="B61" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D61" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="62" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A62" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="B62" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C62" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D62" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="63" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A63" s="3" t="s">
+        <v>75</v>
+      </c>
+      <c r="B63" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C7" s="7" t="s">
+      <c r="C63" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D63" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A64" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="B64" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D7" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="6" t="s">
+      <c r="C64" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="65" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A65" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="B65" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D65" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="66" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A66" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="B66" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="3" t="s">
-        <v>107</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E8" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
-        <v>108</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
-        <v>109</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>10</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E10" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
-        <v>110</v>
-      </c>
-      <c r="B11" s="7" t="s">
+      <c r="C66" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D66" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="67" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A67" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="B67" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="7" t="s">
+      <c r="C67" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D67" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="68" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A68" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="B68" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D11" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="E11" s="6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D12" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D13" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C14" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D14" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C16" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D16" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A17" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C17" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D18" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A19" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D19" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A20" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="B20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C20" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D20" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A21" s="3" t="s">
-        <v>19</v>
-      </c>
-      <c r="B21" s="4" t="s">
+      <c r="C68" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D68" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A69" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="B69" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C21" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="B22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C22" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A23" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="B23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C23" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="B24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D24" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A25" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="B25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E25" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A26" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C26" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A27" s="3" t="s">
-        <v>25</v>
-      </c>
-      <c r="B27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C27" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D27" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E27" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A28" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="B28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E28" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A29" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="B29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C29" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A30" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="B30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C30" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D30" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A31" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="B31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C31" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A32" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="B32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C32" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D32" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E32" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A33" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C33" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D33" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E33" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A34" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C34" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E34" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A35" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="B35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D35" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E35" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A36" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="B36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C36" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D36" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E36" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A37" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="B37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C37" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D37" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E37" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A38" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="B38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C38" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D38" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E38" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A39" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C39" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D39" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E39" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A40" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D40" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E40" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A41" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E41" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A42" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E42" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A43" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C43" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E43" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A44" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="B44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C44" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E44" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A45" s="3" t="s">
-        <v>43</v>
-      </c>
-      <c r="B45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C45" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E45" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A46" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="B46" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C46" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D46" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E46" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A47" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C47" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D47" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E47" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A48" s="3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C48" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D48" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E48" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A49" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C49" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D49" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E49" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A50" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="B50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C50" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D50" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E50" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A51" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="B51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C51" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D51" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E51" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A52" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B52" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="C52" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D52" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E52" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A53" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="B53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E53" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A54" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="B54" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C54" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E54" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A55" s="3" t="s">
-        <v>53</v>
-      </c>
-      <c r="B55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C55" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D55" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E55" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A56" s="3" t="s">
-        <v>54</v>
-      </c>
-      <c r="B56" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D56" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E56" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A57" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="B57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D57" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E57" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A58" s="3" t="s">
-        <v>56</v>
-      </c>
-      <c r="B58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D58" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E58" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A59" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="B59" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D59" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E59" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A60" s="3" t="s">
-        <v>58</v>
-      </c>
-      <c r="B60" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D60" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E60" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A61" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="B61" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D61" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E61" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A62" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="B62" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D62" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E62" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A63" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="B63" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C63" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D63" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E63" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A64" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="B64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D64" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E64" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A65" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="B65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D65" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E65" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A66" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="B66" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D66" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E66" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A67" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="B67" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D67" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E67" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A68" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="B68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D68" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E68" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A69" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="B69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D69" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E69" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C69" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D69" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="70" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A70" s="3" t="s">
         <v>68</v>
       </c>
       <c r="B70" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C70" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D70" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B71" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D71" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="72" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A72" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="B72" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C72" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D72" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="73" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A73" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="B73" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C73" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D73" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="74" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A74" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="B74" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C74" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D74" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A75" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="B75" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C75" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D75" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="76" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A76" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C76" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D76" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="77" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A77" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="B77" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D77" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A78" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="B78" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D78" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A79" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="B79" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C79" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D79" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A80" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="B80" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D80" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A81" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="B81" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C81" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D81" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A82" s="3" t="s">
+        <v>56</v>
+      </c>
+      <c r="B82" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C82" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D82" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="83" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A83" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="B83" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C83" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D83" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="84" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A84" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="B84" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C84" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D84" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="85" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A85" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="B85" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C85" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D85" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="86" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A86" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="B86" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C86" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D86" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="87" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A87" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="B87" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C87" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D87" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="88" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A88" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="B88" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D70" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E70" s="5" t="s">
+      <c r="C88" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D88" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="89" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A89" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="B89" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A71" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="B71" s="4" t="s">
+      <c r="C89" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D89" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="90" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A90" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="B90" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="C90" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D90" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="91" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A91" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="B91" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="4" t="s">
+      <c r="C91" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D91" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="92" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A92" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="B92" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D71" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E71" s="5" t="s">
+      <c r="C92" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D92" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="93" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A93" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="B93" s="4" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A72" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="B72" s="4" t="s">
+      <c r="C93" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D93" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A94" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B94" s="4" t="s">
+        <v>9</v>
+      </c>
+      <c r="C94" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D94" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A95" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B95" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C95" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D95" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="96" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A96" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="B96" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C96" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D96" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="97" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A97" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B97" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C97" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D97" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="98" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A98" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B98" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C72" s="4" t="s">
+      <c r="C98" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D98" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="99" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A99" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B99" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C99" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D99" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A100" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D72" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E72" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A73" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="B73" s="4" t="s">
+      <c r="C100" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D100" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="101" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A101" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B101" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="C73" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D73" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E73" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A74" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="B74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D74" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E74" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A75" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="B75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D75" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E75" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A76" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="B76" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D76" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E76" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A77" s="3" t="s">
-        <v>75</v>
-      </c>
-      <c r="B77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D77" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E77" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A78" s="3" t="s">
-        <v>76</v>
-      </c>
-      <c r="B78" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="D78" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E78" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A79" s="3" t="s">
-        <v>78</v>
-      </c>
-      <c r="B79" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C79" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D79" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E79" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A80" s="3" t="s">
-        <v>79</v>
-      </c>
-      <c r="B80" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C80" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D80" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E80" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A81" s="3" t="s">
-        <v>80</v>
-      </c>
-      <c r="B81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C81" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D81" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E81" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A82" s="3" t="s">
-        <v>81</v>
-      </c>
-      <c r="B82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C82" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D82" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E82" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A83" s="3" t="s">
-        <v>82</v>
-      </c>
-      <c r="B83" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C83" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D83" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E83" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A84" s="3" t="s">
-        <v>83</v>
-      </c>
-      <c r="B84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C84" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D84" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E84" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A85" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="B85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C85" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D85" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E85" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A86" s="3" t="s">
-        <v>85</v>
-      </c>
-      <c r="B86" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C86" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D86" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E86" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A87" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="B87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C87" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D87" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E87" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A88" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="B88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C88" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D88" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E88" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A89" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="B89" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C89" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D89" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E89" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A90" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="B90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C90" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D90" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E90" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A91" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="B91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C91" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D91" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E91" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A92" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="B92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D92" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E92" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A93" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="B93" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C93" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D93" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E93" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A94" s="3" t="s">
-        <v>93</v>
-      </c>
-      <c r="B94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="C94" s="4" t="s">
-        <v>10</v>
-      </c>
-      <c r="D94" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E94" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A95" s="3" t="s">
-        <v>94</v>
-      </c>
-      <c r="B95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C95" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D95" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E95" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A96" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="B96" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C96" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D96" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E96" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A97" s="3" t="s">
-        <v>96</v>
-      </c>
-      <c r="B97" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C97" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D97" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E97" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A98" s="3" t="s">
-        <v>97</v>
-      </c>
-      <c r="B98" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D98" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E98" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A99" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="B99" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="C99" s="4" t="s">
-        <v>8</v>
-      </c>
-      <c r="D99" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E99" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A100" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="B100" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C100" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D100" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E100" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A101" s="3" t="s">
-        <v>100</v>
-      </c>
-      <c r="B101" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="D101" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="E101" s="5" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C101" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D101" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="102" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B102" s="5"/>
     </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B103" s="5"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B104" s="5"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B105" s="5"/>
     </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B106" s="5"/>
     </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B107" s="5"/>
     </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B108" s="5"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B109" s="5"/>
     </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B110" s="5"/>
     </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B111" s="5"/>
     </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:4" x14ac:dyDescent="0.25">
       <c r="B112" s="5"/>
     </row>
     <row r="113" spans="2:2" x14ac:dyDescent="0.25">
